--- a/public/assets/Sample_File.xlsx
+++ b/public/assets/Sample_File.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BIT projects\WhatsappFE\WhatsappFE\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{342EBF57-7C98-4F71-BF01-9DB4527E7E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC7EE45-D9CD-47DE-B98A-C59EB1296CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{E0324973-91B0-4F26-8F47-A3FDD94BA5D7}"/>
   </bookViews>
@@ -502,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="1">
-        <v>96599310864</v>
+        <v>96595574676</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">

--- a/public/assets/Sample_File.xlsx
+++ b/public/assets/Sample_File.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BIT projects\WhatsappFE\WhatsappFE\public\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC7EE45-D9CD-47DE-B98A-C59EB1296CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5DF760-5F2D-4330-88C6-AC5BE193A450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{E0324973-91B0-4F26-8F47-A3FDD94BA5D7}"/>
+    <workbookView xWindow="690" yWindow="690" windowWidth="21600" windowHeight="11385" xr2:uid="{E0324973-91B0-4F26-8F47-A3FDD94BA5D7}"/>
   </bookViews>
   <sheets>
     <sheet name="ContactReport" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F025F-E6F6-4088-98CF-4BDE69818CD4}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -509,13 +509,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
